--- a/Hoadon/HD2026/HDVao/5/3502323472_HDDienTuKhongMa.xlsx
+++ b/Hoadon/HD2026/HDVao/5/3502323472_HDDienTuKhongMa.xlsx
@@ -213,7 +213,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Từ ngày 01/05/2026 đến ngày 06/05/2026</t>
+          <t>Từ ngày 01/05/2026 đến ngày 07/05/2026</t>
         </is>
       </c>
     </row>
